--- a/uploads/Mapping_Format.xlsx
+++ b/uploads/Mapping_Format.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\garre\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE157B73-0434-464A-92EF-A3692D3BDDA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{B7F4EB09-CE84-42B2-B475-54611CF611B0}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8496"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,27 +24,72 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>Faculty ID</t>
-  </si>
-  <si>
-    <t>Form Access</t>
-  </si>
-  <si>
-    <t>Student ID</t>
-  </si>
-  <si>
-    <t>FAC66600</t>
-  </si>
-  <si>
-    <t>FAC23400</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+  <si>
+    <t>Skill Name</t>
+  </si>
+  <si>
+    <t>Student Name</t>
+  </si>
+  <si>
+    <t>gargi</t>
+  </si>
+  <si>
+    <t>gehna</t>
+  </si>
+  <si>
+    <t>Garret</t>
+  </si>
+  <si>
+    <t>Suppi</t>
+  </si>
+  <si>
+    <t>Gargi</t>
+  </si>
+  <si>
+    <t>IM INJECTION</t>
+  </si>
+  <si>
+    <t>IV INSERTION</t>
+  </si>
+  <si>
+    <t>NASOGASTRIC (NG) TUBE INSERTION PROCEDURE</t>
+  </si>
+  <si>
+    <t>gargimittal</t>
+  </si>
+  <si>
+    <t>garret</t>
+  </si>
+  <si>
+    <t>supra</t>
+  </si>
+  <si>
+    <t>FAC456</t>
+  </si>
+  <si>
+    <t>FAC567</t>
+  </si>
+  <si>
+    <t>FAC678</t>
+  </si>
+  <si>
+    <t>faculty_id</t>
+  </si>
+  <si>
+    <t>faculty_name</t>
+  </si>
+  <si>
+    <t>skill_id</t>
+  </si>
+  <si>
+    <t>student_id</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -390,76 +434,143 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F976A7C7-0FCD-49CA-A779-4FFB2D81B209}">
-  <dimension ref="A1:C7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="12.109375" customWidth="1"/>
+    <col min="3" max="4" width="12.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="E1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
+        <v>13</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B3">
+      <c r="D2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2">
         <v>2</v>
       </c>
-      <c r="C3">
+      <c r="F2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E3">
+        <v>3</v>
+      </c>
+      <c r="F3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E6">
+        <v>3</v>
+      </c>
+      <c r="F6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B4">
+      <c r="F8" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>14</v>
+      </c>
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9">
         <v>3</v>
       </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>2</v>
-      </c>
-      <c r="C5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+      <c r="F9" t="s">
         <v>4</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
